--- a/data/england/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/england/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN2"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,84 +762,82 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45523.66666666666</v>
+        <v>45528.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>32261</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31977</v>
-      </c>
+        <v>42789</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.15</v>
+        <v>1.96</v>
       </c>
       <c r="L2" t="n">
-        <v>0.98</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="N2" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,130 +852,3538 @@
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>25.9</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="AD2" t="n">
-        <v>181.7</v>
+        <v>184</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.3</v>
+        <v>2.090909090909091</v>
       </c>
       <c r="AF2" t="n">
-        <v>75</v>
+        <v>79.72727272727273</v>
       </c>
       <c r="AG2" t="n">
-        <v>7580000</v>
+        <v>25054545.45454545</v>
       </c>
       <c r="AH2" t="n">
-        <v>78.5</v>
+        <v>81.90909090909091</v>
       </c>
       <c r="AI2" t="n">
-        <v>24.66666666666667</v>
+        <v>23.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>185.2222222222222</v>
+        <v>183.375</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.888888888888889</v>
+        <v>2.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>81.33333333333333</v>
+        <v>84</v>
       </c>
       <c r="AM2" t="n">
-        <v>38444444.44444445</v>
+        <v>67000000</v>
       </c>
       <c r="AN2" t="n">
-        <v>84.77777777777777</v>
+        <v>87.75</v>
       </c>
       <c r="AO2" t="n">
-        <v>25</v>
+        <v>23.90476190476191</v>
       </c>
       <c r="AP2" t="n">
-        <v>179.8125</v>
+        <v>181.2857142857143</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.25</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AR2" t="n">
-        <v>72.875</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="AS2" t="n">
-        <v>5842187.5</v>
+        <v>12909523.80952381</v>
       </c>
       <c r="AT2" t="n">
-        <v>77.3125</v>
+        <v>80.38095238095238</v>
       </c>
       <c r="AU2" t="n">
-        <v>23.47619047619047</v>
+        <v>24.21428571428572</v>
       </c>
       <c r="AV2" t="n">
-        <v>183.4761904761905</v>
+        <v>177.2857142857143</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.952380952380952</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AX2" t="n">
-        <v>78.04761904761905</v>
+        <v>78.85714285714286</v>
       </c>
       <c r="AY2" t="n">
-        <v>26341666.66666667</v>
+        <v>29892857.14285714</v>
       </c>
       <c r="AZ2" t="n">
-        <v>83.14285714285714</v>
+        <v>83.78571428571429</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>26.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
         <v>2</v>
       </c>
       <c r="BE2" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="BF2" t="n">
-        <v>10100000</v>
+        <v>52000000</v>
       </c>
       <c r="BG2" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="BH2" t="n">
-        <v>30.5</v>
+        <v>24.75</v>
       </c>
       <c r="BI2" t="n">
-        <v>191.5</v>
+        <v>179.25</v>
       </c>
       <c r="BJ2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>318</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22099</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M3" t="n">
+        <v>59</v>
+      </c>
+      <c r="N3" t="n">
+        <v>41</v>
+      </c>
+      <c r="O3" t="n">
+        <v>14</v>
+      </c>
+      <c r="P3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2</v>
       </c>
-      <c r="BL2" t="n">
-        <v>154</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>25475000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>157</v>
-      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>17</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>48</v>
+      </c>
+      <c r="X3" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>183.2222222222222</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>79.22222222222223</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>20333333.33333333</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>80.88888888888889</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>183</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>74.58333333333333</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6875000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>27.94444444444444</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>180.8333333333333</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>80.22222222222223</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>74</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25401</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M4" t="n">
+        <v>55</v>
+      </c>
+      <c r="N4" t="n">
+        <v>45</v>
+      </c>
+      <c r="O4" t="n">
+        <v>18</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="n">
+        <v>13</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>48</v>
+      </c>
+      <c r="X4" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>184</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11410000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>7580000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6090000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>178.65</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7018750</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>211</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M5" t="n">
+        <v>76</v>
+      </c>
+      <c r="N5" t="n">
+        <v>24</v>
+      </c>
+      <c r="O5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>15</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>48</v>
+      </c>
+      <c r="X5" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>71150000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>4160000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>25.73684210526316</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>182.4736842105263</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2.210526315789474</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>80.84210526315789</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>42526315.78947368</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>84.47368421052632</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>25.08695652173913</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>182.4782608695652</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>69.1304347826087</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2365217.391304348</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>73.04347826086956</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>158</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>132400000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>174</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>181.1666666666667</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>426</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>21800000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F6" t="n">
+        <v>31150</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M6" t="n">
+        <v>65</v>
+      </c>
+      <c r="N6" t="n">
+        <v>35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14</v>
+      </c>
+      <c r="T6" t="n">
+        <v>13</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>48</v>
+      </c>
+      <c r="X6" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>25.55555555555556</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4811111.111111111</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>10210000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>179.0555555555555</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>68.05555555555556</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2797222.222222222</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>25.78947368421053</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>187</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>75.84210526315789</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10510526.31578947</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>79.31578947368421</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>280</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>308</v>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F7" t="n">
+        <v>61357</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M7" t="n">
+        <v>71</v>
+      </c>
+      <c r="N7" t="n">
+        <v>29</v>
+      </c>
+      <c r="O7" t="n">
+        <v>13</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11</v>
+      </c>
+      <c r="T7" t="n">
+        <v>15</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>48</v>
+      </c>
+      <c r="X7" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>24.22222222222222</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>80.66666666666667</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>38644444.44444445</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>85.11111111111111</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>183</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>10260000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>184.2777777777778</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>76.72222222222223</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>19348611.11111111</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>83.05555555555556</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>25.41666666666667</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>185.9166666666667</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8970833.333333334</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>76.16666666666667</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>159</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>164</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>443</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>40625000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45528.35416666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31537</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M8" t="n">
+        <v>48</v>
+      </c>
+      <c r="N8" t="n">
+        <v>52</v>
+      </c>
+      <c r="O8" t="n">
+        <v>14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>13</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>48</v>
+      </c>
+      <c r="X8" t="n">
+        <v>481</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>78.77777777777777</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>82</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>39625000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>22.04545454545455</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>177.0909090909091</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>71.95454545454545</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7793181.818181818</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>81</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>184.5833333333333</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>77.16666666666667</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>81.58333333333333</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>230</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>254</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>316</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>92000000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>23e0sUpB</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>31367</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14769</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O9" t="n">
+        <v>21</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>16</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>48</v>
+      </c>
+      <c r="X9" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2040000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>26.57142857142857</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>182.4285714285714</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>68.21428571428571</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1603571.428571429</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>26.14285714285714</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>183</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>65.71428571428571</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1014285.714285714</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>69.57142857142857</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>134</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>148</v>
+      </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>prkJckVi</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donohue m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>34742</v>
+      </c>
+      <c r="F10" t="n">
+        <v>26270</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>67</v>
+      </c>
+      <c r="N10" t="n">
+        <v>33</v>
+      </c>
+      <c r="O10" t="n">
+        <v>31</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="n">
+        <v>15</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>48</v>
+      </c>
+      <c r="X10" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2520000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>21.35714285714286</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>181.5714285714286</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>64.85714285714286</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1605714.285714286</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>75.64285714285714</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>139</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>6cwSeTa4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carrow road
+  norwich </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>27137</v>
+      </c>
+      <c r="F11" t="n">
+        <v>26373</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>53</v>
+      </c>
+      <c r="N11" t="n">
+        <v>47</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>48</v>
+      </c>
+      <c r="X11" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>69.11111111111111</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>3191666.666666667</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>76.88888888888889</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1613888.888888889</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>20.92307692307692</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>179.4615384615385</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>65.46153846153847</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2605769.230769231</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>75.84615384615384</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>33</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>186</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>71</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>130</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ENtzf7UG</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whitestone d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deepdale
+  preston </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23408</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15245</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>43</v>
+      </c>
+      <c r="N12" t="n">
+        <v>57</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>18</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>48</v>
+      </c>
+      <c r="X12" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>186.375</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>6175000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2920000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>68.06666666666666</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>72.73333333333333</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1503750</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>363</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>16400000</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6BI0ASEc</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bet365 stadium
+  stoke on trent </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>30089</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24371</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>51</v>
+      </c>
+      <c r="N13" t="n">
+        <v>49</v>
+      </c>
+      <c r="O13" t="n">
+        <v>10</v>
+      </c>
+      <c r="P13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>48</v>
+      </c>
+      <c r="X13" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>23.125</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>181.375</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>67.625</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1893750</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>73.625</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2320000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>23.95238095238095</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>182</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>68.47619047619048</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2058809.523809524</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>73.85714285714286</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>24.4375</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>2375000</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>74</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>278</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>279</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>188</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>70</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>EyM886qA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">martin s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium of light
+  sunderland </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48707</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40096</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>39</v>
+      </c>
+      <c r="N14" t="n">
+        <v>61</v>
+      </c>
+      <c r="O14" t="n">
+        <v>15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>19</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>48</v>
+      </c>
+      <c r="X14" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>21.77777777777778</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2413888.888888889</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>4444444.444444444</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>23.42105263157895</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>182.2105263157895</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2328947.368421053</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>74.78947368421052</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>186.8571428571429</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>69.85714285714286</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2914285.714285714</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>77.28571428571429</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>155</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>445</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>43100000</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YPYtjbTr</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarage road
+  watford </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>68</v>
+      </c>
+      <c r="N15" t="n">
+        <v>32</v>
+      </c>
+      <c r="O15" t="n">
+        <v>12</v>
+      </c>
+      <c r="P15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="n">
+        <v>11</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>48</v>
+      </c>
+      <c r="X15" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1788888.888888889</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1738888.888888889</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zHg8u8FN</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.35416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>21454</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>51</v>
+      </c>
+      <c r="N16" t="n">
+        <v>49</v>
+      </c>
+      <c r="O16" t="n">
+        <v>13</v>
+      </c>
+      <c r="P16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>18</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>48</v>
+      </c>
+      <c r="X16" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2087500</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>3860000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1484722.222222222</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>73.27777777777777</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>25.0625</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>179</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>2212500</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>73.4375</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>185</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IycXZowo</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.35416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>25586</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20009</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>71</v>
+      </c>
+      <c r="N17" t="n">
+        <v>29</v>
+      </c>
+      <c r="O17" t="n">
+        <v>14</v>
+      </c>
+      <c r="P17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="n">
+        <v>16</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>48</v>
+      </c>
+      <c r="X17" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>177.8888888888889</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>2025000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>20.57142857142857</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>179.9285714285714</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>63.92857142857143</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2096071.428571429</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>74.85714285714286</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>180.5714285714286</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>68</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1335714.285714286</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>71.14285714285714</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>181</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>198</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5125000</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>227</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>143</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fXlrhoaT</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45528.35416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loftus road
+  london </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>18439</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15285</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>55</v>
+      </c>
+      <c r="N18" t="n">
+        <v>45</v>
+      </c>
+      <c r="O18" t="n">
+        <v>31</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="n">
+        <v>14</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>48</v>
+      </c>
+      <c r="X18" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2095000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>20.83333333333333</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>182.1666666666667</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>59.33333333333334</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>712500</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>23.8125</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>67.1875</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1810937.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>212</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>213</v>
+      </c>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>j3zEnPMj</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45527.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hillsborough
+  sheffield </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>39732</v>
+      </c>
+      <c r="F19" t="n">
+        <v>28800</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>30</v>
+      </c>
+      <c r="N19" t="n">
+        <v>70</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>10</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>48</v>
+      </c>
+      <c r="X19" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1556250</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>185</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>6462500</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>78.625</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>26.59090909090909</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>66.27272727272727</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1181818.181818182</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>70.40909090909091</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>182</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>72.09090909090909</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4545454.545454546</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>35</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>193</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>150000</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/england/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BL28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,280 +480,270 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_away</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>ball_possession_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ball_possession_away</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_away</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_away</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>fouls_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>fouls_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>id_team_home_rival_team</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>id_team_away_rival_team</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_sub_away</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_away</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_int_rep_player_miss_home</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_val_player_miss_home</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_int_rep_player_miss_away</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_val_player_miss_away</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
@@ -762,174 +752,82 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>vDEpovX1</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.52083333334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attwell s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>61276</v>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>42DzSumJ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>fBo5RVhP</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.31</v>
+        <v>48</v>
       </c>
       <c r="L2" t="n">
-        <v>0.55</v>
+        <v>483</v>
       </c>
       <c r="M2" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>38</v>
-      </c>
-      <c r="O2" t="n">
-        <v>19</v>
-      </c>
-      <c r="P2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>10</v>
-      </c>
-      <c r="T2" t="n">
-        <v>7</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>48</v>
-      </c>
-      <c r="X2" t="n">
-        <v>481</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>59500000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>25.72727272727273</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>184.5454545454545</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>76.27272727272727</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>10918181.81818182</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>79.09090909090909</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>23.91304347826087</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>181.695652173913</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.869565217391304</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>79.56521739130434</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>31817391.30434782</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>84.17391304347827</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>178.5333333333333</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.266666666666667</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8285000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>80.53333333333333</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
@@ -937,64 +835,48 @@
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>153</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>160</v>
-      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>hxlYyYo4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45532.66666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">allison s 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11307</v>
+        <v>30404</v>
       </c>
       <c r="F3" t="n">
-        <v>11161</v>
+        <v>23083</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1003,586 +885,4158 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.01</v>
+        <v>48</v>
       </c>
       <c r="L3" t="n">
-        <v>1.96</v>
+        <v>484</v>
       </c>
       <c r="M3" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>61</v>
+        <v>20242025</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="S3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>13</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>hbOpz9hE</t>
         </is>
       </c>
-      <c r="W3" t="n">
-        <v>48</v>
-      </c>
-      <c r="X3" t="n">
-        <v>481</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>WSzc94ws</t>
         </is>
       </c>
-      <c r="AC3" t="n">
-        <v>24.77777777777778</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>179.8888888888889</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.222222222222222</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>75.33333333333333</v>
-      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>8233333.333333333</v>
+        <v>26.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>78.88888888888889</v>
+        <v>185.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>26.3</v>
+        <v>1.9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>187.3</v>
+        <v>79.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>28360000</v>
       </c>
       <c r="AL3" t="n">
-        <v>78.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>22330000</v>
+        <v>23.5625</v>
       </c>
       <c r="AN3" t="n">
-        <v>80.8</v>
+        <v>184.0625</v>
       </c>
       <c r="AO3" t="n">
-        <v>21.83333333333333</v>
+        <v>1.5625</v>
       </c>
       <c r="AP3" t="n">
-        <v>180.0555555555555</v>
+        <v>75.5625</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>11762500</v>
       </c>
       <c r="AR3" t="n">
-        <v>72.55555555555556</v>
+        <v>80.5625</v>
       </c>
       <c r="AS3" t="n">
-        <v>7788888.888888889</v>
+        <v>25.9375</v>
       </c>
       <c r="AT3" t="n">
-        <v>80.33333333333333</v>
+        <v>181.75</v>
       </c>
       <c r="AU3" t="n">
-        <v>25.94736842105263</v>
+        <v>1.4375</v>
       </c>
       <c r="AV3" t="n">
-        <v>180.4736842105263</v>
+        <v>79.125</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.473684210526316</v>
+        <v>28105000</v>
       </c>
       <c r="AX3" t="n">
-        <v>76.31578947368421</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>16646315.78947368</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>80.36842105263158</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>180.6666666666667</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>232</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>237</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>24.85714285714286</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>186.4285714285714</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1.857142857142857</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>540</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>188375000</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>576</v>
-      </c>
+        <v>81.5625</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>U32wGjPp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45532.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">england d 
+          <t xml:space="preserve">linington j 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">the cherry red records stadium
+  london </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31750</v>
+        <v>9215</v>
       </c>
       <c r="F4" t="n">
-        <v>31235</v>
+        <v>7934</v>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2.16</v>
+        <v>48</v>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>484</v>
       </c>
       <c r="M4" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>62</v>
+        <v>20242025</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
         <v>13</v>
       </c>
-      <c r="T4" t="n">
-        <v>13</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>48</v>
-      </c>
-      <c r="X4" t="n">
-        <v>481</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>20242025</v>
+      <c r="V4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
       </c>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>182.125</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>77.125</v>
-      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>13137500</v>
+        <v>26</v>
       </c>
       <c r="AH4" t="n">
-        <v>79.625</v>
+        <v>184.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.9</v>
+        <v>1.125</v>
       </c>
       <c r="AJ4" t="n">
-        <v>183.1</v>
+        <v>71</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>3537500</v>
       </c>
       <c r="AL4" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>24050000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>27.88235294117647</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>178.7058823529412</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.529411764705882</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>76.29411764705883</v>
-      </c>
+        <v>73.625</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>9617647.05882353</v>
+        <v>24.04545454545455</v>
       </c>
       <c r="AT4" t="n">
-        <v>78</v>
+        <v>181.8636363636364</v>
       </c>
       <c r="AU4" t="n">
-        <v>23.3125</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="AV4" t="n">
-        <v>180</v>
+        <v>69.22727272727273</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.5625</v>
+        <v>2796590.909090909</v>
       </c>
       <c r="AX4" t="n">
-        <v>79.25</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>29906250</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>188.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>156</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>158</v>
-      </c>
+        <v>75.22727272727273</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>pKIPNiIj</t>
+          <t>hGzqjO6E</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.45833333334</v>
+        <v>45532.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">langford o 
+          <t xml:space="preserve">nield t 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21088</v>
+        <v>33280</v>
       </c>
       <c r="F5" t="n">
-        <v>20174</v>
+        <v>7225</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>48</v>
+      </c>
+      <c r="L5" t="n">
+        <v>484</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="n">
+        <v>27</v>
+      </c>
+      <c r="P5" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>10</v>
+      </c>
+      <c r="R5" t="n">
+        <v>13</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>K6xezbY7</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>58</v>
-      </c>
-      <c r="N5" t="n">
-        <v>42</v>
-      </c>
-      <c r="O5" t="n">
-        <v>9</v>
-      </c>
-      <c r="P5" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>14</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>OEy2L7Zo</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>48</v>
-      </c>
-      <c r="X5" t="n">
-        <v>485</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>24.46153846153846</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>178.7692307692308</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>68.46153846153847</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3392307.692307692</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>77.30769230769231</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45532.65625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">howard p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10105</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6716</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>xYu73rNn</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>48</v>
+      </c>
+      <c r="L6" t="n">
+        <v>484</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="n">
+        <v>27</v>
+      </c>
+      <c r="P6" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>13</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>MiVxbVgA</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>23.05555555555556</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>72.61111111111111</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7887500</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>77.77777777777777</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45532.65625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toner b 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>21088</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>hl2V5JIl</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>48</v>
+      </c>
+      <c r="L7" t="n">
+        <v>484</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="n">
+        <v>73</v>
+      </c>
+      <c r="P7" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>12</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>65pf39vc</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>26.64285714285714</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>176.8571428571429</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>67.78571428571429</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1387500</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>71.35714285714286</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45532.65625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F8" t="n">
+        <v>47381</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>48</v>
+      </c>
+      <c r="L8" t="n">
+        <v>484</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="n">
+        <v>46</v>
+      </c>
+      <c r="P8" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" t="n">
+        <v>13</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>15</v>
+      </c>
+      <c r="V8" t="n">
+        <v>13</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>18425000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>181.2222222222222</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>6966666.666666667</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>79.22222222222223</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>25.11764705882353</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>182.0588235294118</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.117647058823529</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>78.76470588235294</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>22947058.82352941</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>82.05882352941177</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>22.88235294117647</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>178.2352941176471</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>74.05882352941177</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8494117.647058824</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>79.47058823529412</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45532.64583333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>31750</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19236</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>48</v>
+      </c>
+      <c r="L9" t="n">
+        <v>484</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="n">
+        <v>52</v>
+      </c>
+      <c r="P9" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>17</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>14</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>7512500</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>78</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>185.2222222222222</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3055555.555555556</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>27.47058823529412</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>179.8235294117647</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.470588235294118</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>76.17647058823529</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>9835294.117647059</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>78.17647058823529</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>71.91666666666667</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4525000</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45531.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stroud k 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  andrew s stadium
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29409</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11949</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SWk4muv7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L10" t="n">
+        <v>484</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="n">
+        <v>58</v>
+      </c>
+      <c r="P10" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>16</v>
+      </c>
+      <c r="R10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>18</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Uu6L6Igl</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>6320000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>25.92857142857143</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>177.7857142857143</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>67.35714285714286</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1576785.714285714</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>70.85714285714286</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>182.95</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>9435000</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45531.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donohue m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12503</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>48</v>
+      </c>
+      <c r="L11" t="n">
+        <v>484</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="n">
+        <v>43</v>
+      </c>
+      <c r="P11" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>13</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>13</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>181.7777777777778</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>77</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>15088888.88888889</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>25.94736842105263</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>184.1052631578947</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8157894.736842105</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>78.42105263157895</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>26.41666666666667</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>71.91666666666667</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2841666.666666667</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reeves t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oakwell
+  barnsley </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23287</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10739</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UNGEKMx6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>48</v>
+      </c>
+      <c r="L12" t="n">
+        <v>484</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="n">
+        <v>34</v>
+      </c>
+      <c r="P12" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>20</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>14</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>bNLzN2wB</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2378125</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>181</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>68.85714285714286</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3255357.142857143</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>75.64285714285714</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stockbridge s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3003</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>KKJL7QXd</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>48</v>
+      </c>
+      <c r="L13" t="n">
+        <v>484</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="n">
+        <v>47</v>
+      </c>
+      <c r="P13" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>13</v>
+      </c>
+      <c r="R13" t="n">
+        <v>11</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>14</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>joDBK9gn</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>63.125</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>859375</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>31367</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9418</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8EFIJthC</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>48</v>
+      </c>
+      <c r="L14" t="n">
+        <v>484</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="n">
+        <v>61</v>
+      </c>
+      <c r="P14" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>14</v>
+      </c>
+      <c r="R14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>19</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2e9kg9n1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1694444.444444444</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>73</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>182.7222222222222</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>68.83333333333333</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1619444.444444444</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>67</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1141666.666666667</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chilowicz a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F15" t="n">
+        <v>19175</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>QVmLl54o</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>48</v>
+      </c>
+      <c r="L15" t="n">
+        <v>484</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="n">
+        <v>45</v>
+      </c>
+      <c r="P15" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>17</v>
+      </c>
+      <c r="R15" t="n">
+        <v>9</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10</v>
+      </c>
+      <c r="V15" t="n">
+        <v>16</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>COqtASrJ</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>21.125</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>178.25</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>6331250</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>81</v>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="n">
+        <v>21.86666666666667</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>176.5333333333333</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>68.86666666666666</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8218333.333333333</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>78.06666666666666</v>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">finnie w 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coventry building society arena
+  coventry </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>32753</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11808</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>48</v>
+      </c>
+      <c r="L16" t="n">
+        <v>484</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="n">
+        <v>53</v>
+      </c>
+      <c r="P16" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>18</v>
+      </c>
+      <c r="R16" t="n">
+        <v>8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>15</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2412500</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="n">
+        <v>23.95238095238095</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>71.47619047619048</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4709523.80952381</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>77</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37245</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>hlzYDy5q</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>48</v>
+      </c>
+      <c r="L17" t="n">
+        <v>484</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="n">
+        <v>58</v>
+      </c>
+      <c r="P17" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>16</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>16</v>
+      </c>
+      <c r="V17" t="n">
+        <v>10</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>pSZhI8SM</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>185.7777777777778</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>74.77777777777777</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9344444.444444444</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>78.33333333333333</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="n">
+        <v>29.3125</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>178.8125</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.5625</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4898437.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>76</v>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joyce r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5327</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1744</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>tCZ3D68d</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>KMfM7P4b</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>48</v>
+      </c>
+      <c r="L18" t="n">
+        <v>484</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="n">
+        <v>46</v>
+      </c>
+      <c r="P18" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>15</v>
+      </c>
+      <c r="R18" t="n">
+        <v>16</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>11</v>
+      </c>
+      <c r="V18" t="n">
+        <v>12</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>13817500</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corlett m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>9052</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6364</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OEaiS3za</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>48</v>
+      </c>
+      <c r="L19" t="n">
+        <v>484</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="n">
+        <v>30</v>
+      </c>
+      <c r="P19" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>13</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>12</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SGvTSGmc</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>942500</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>26.57894736842105</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>179.2105263157895</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>67.89473684210526</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1405263.157894737</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>71.31578947368421</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">speedie b 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">envirovent stadium
+  harrogate </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2570</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CQv5qrFt</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>48</v>
+      </c>
+      <c r="L20" t="n">
+        <v>484</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="n">
+        <v>33</v>
+      </c>
+      <c r="P20" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>15</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>ANwVL1Tp</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>184</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1687500</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>23.36842105263158</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>184.2105263157895</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>69.05263157894737</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3768421.052631579</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>75.47368421052632</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13011</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>jVhkb1QE</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>48</v>
+      </c>
+      <c r="L21" t="n">
+        <v>484</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="n">
+        <v>74</v>
+      </c>
+      <c r="P21" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>24</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2L1wFbM5</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>8697500</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>77</v>
+      </c>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="n">
+        <v>23.85714285714286</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>180.0714285714286</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5669642.857142857</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>76.85714285714286</v>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rock d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the den
+  london </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>20146</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5875</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>KKyYcus9</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>48</v>
+      </c>
+      <c r="L22" t="n">
+        <v>484</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="n">
+        <v>56</v>
+      </c>
+      <c r="P22" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>18</v>
+      </c>
+      <c r="V22" t="n">
+        <v>20</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C6Wq1Q6e</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="n">
+        <v>26.42105263157895</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>177.8421052631579</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>68</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1638157.894736842</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>72.73684210526316</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>20.18181818181818</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>60.45454545454545</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>756818.1818181818</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doughty l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loftus road
+  london </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>18439</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7132</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>48</v>
+      </c>
+      <c r="L23" t="n">
+        <v>484</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="n">
+        <v>49</v>
+      </c>
+      <c r="P23" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>11</v>
+      </c>
+      <c r="R23" t="n">
+        <v>22</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>15</v>
+      </c>
+      <c r="V23" t="n">
+        <v>15</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>69.90909090909091</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2602272.727272727</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>74.54545454545455</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>68.16666666666667</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1535416.666666667</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>71.58333333333333</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>182</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>70.05555555555556</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1961111.111111111</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>71.72222222222223</v>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gill s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>9877</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3220</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>EqfQ6qK4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Or1bBrWD</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>48</v>
+      </c>
+      <c r="L24" t="n">
+        <v>484</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="n">
+        <v>38</v>
+      </c>
+      <c r="P24" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>12</v>
+      </c>
+      <c r="R24" t="n">
+        <v>22</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>14</v>
+      </c>
+      <c r="V24" t="n">
+        <v>9</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>EqN1jJFK</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>EosAlOi5</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duckworth e 
+  eng </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>11300</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3378</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>YgrfcLuL</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>48</v>
+      </c>
+      <c r="L25" t="n">
+        <v>484</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="n">
+        <v>37</v>
+      </c>
+      <c r="P25" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>25</v>
+      </c>
+      <c r="R25" t="n">
+        <v>11</v>
+      </c>
+      <c r="S25" t="n">
+        <v>7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>15</v>
+      </c>
+      <c r="V25" t="n">
+        <v>12</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>YTxm48Ng</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>KGX2o9A5</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>64.5625</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1140625</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">davies a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarage road
+  watford </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8319</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>48</v>
+      </c>
+      <c r="L26" t="n">
+        <v>484</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="n">
+        <v>49</v>
+      </c>
+      <c r="P26" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>17</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>19</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>67.77777777777777</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1811111.111111111</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>182.8888888888889</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1452777.777777778</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>183.2222222222222</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>68.88888888888889</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>2077777.777777778</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>23.94444444444444</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>67.38888888888889</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1938888.888888889</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45531.63541666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>34742</v>
+      </c>
+      <c r="F27" t="n">
+        <v>17408</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>48</v>
+      </c>
+      <c r="L27" t="n">
+        <v>484</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="n">
+        <v>63</v>
+      </c>
+      <c r="P27" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>15</v>
+      </c>
+      <c r="R27" t="n">
+        <v>12</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.125</v>
       </c>
-      <c r="AL5" t="n">
-        <v>71.625</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>2575000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>73.625</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>27.47058823529412</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>179</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>66.47058823529412</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>963235.2941176471</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>70.58823529411765</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>24.84615384615385</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>184.2307692307692</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>67</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1432692.307692308</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>70.84615384615384</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>178</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD5" t="n">
+      <c r="AD27" t="n">
+        <v>63.125</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1197500</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>20.125</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1665625</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>76.875</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>22.88888888888889</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>179.9444444444445</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1940555.555555556</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>74.72222222222223</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>67.6875</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2094375</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>73.8125</v>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YqcO2yDl</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45534.66666666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kenilworth road
+  luton </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
         <v>2</v>
       </c>
-      <c r="BE5" t="n">
-        <v>136</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2825000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>141</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>186.3333333333333</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK5" t="n">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>48</v>
+      </c>
+      <c r="L28" t="n">
+        <v>485</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="n">
+        <v>59</v>
+      </c>
+      <c r="P28" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>13</v>
+      </c>
+      <c r="R28" t="n">
+        <v>11</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>14</v>
+      </c>
+      <c r="V28" t="n">
+        <v>11</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2481818.181818182</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>67.6875</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>2273437.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>74.4375</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1292500</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB28" t="n">
         <v>3</v>
       </c>
-      <c r="BL5" t="n">
-        <v>204</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>4100000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>210</v>
+      <c r="BC28" t="n">
+        <v>213</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>221</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>171</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>73</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/england/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP4"/>
+  <dimension ref="A1:CP14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,156 +902,156 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45586.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>61276</v>
+        <v>30404</v>
       </c>
       <c r="F2" t="n">
-        <v>60277</v>
+        <v>29443</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="L2" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="M2" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="n">
         <v>12</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="X2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF2" t="n">
         <v>5</v>
       </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>13</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AG2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH2" t="n">
         <v>12</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>442</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>442</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>364</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>353</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR2" t="n">
         <v>5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>409</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>542</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>325</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>472</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>8</v>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>MeAQUqrN</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AU2" t="n">
@@ -1067,298 +1067,274 @@
         <v>20242025</v>
       </c>
       <c r="AY2" t="n">
-        <v>26.6</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AZ2" t="n">
-        <v>185.1</v>
+        <v>183.4444444444445</v>
       </c>
       <c r="BA2" t="n">
-        <v>83.59999999999999</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="BB2" t="n">
-        <v>129200</v>
+        <v>55111.11111111111</v>
       </c>
       <c r="BC2" t="n">
-        <v>49000000</v>
+        <v>10388888.88888889</v>
       </c>
       <c r="BD2" t="n">
-        <v>85.7</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="BE2" t="n">
-        <v>3</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="BF2" t="n">
-        <v>23.4</v>
+        <v>26.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>184.2</v>
+        <v>182.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>78.3</v>
+        <v>78.625</v>
       </c>
       <c r="BI2" t="n">
-        <v>83700</v>
+        <v>74250</v>
       </c>
       <c r="BJ2" t="n">
-        <v>28975000</v>
+        <v>18637500</v>
       </c>
       <c r="BK2" t="n">
-        <v>83</v>
+        <v>80.375</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BM2" t="n">
-        <v>25.6</v>
+        <v>26</v>
       </c>
       <c r="BN2" t="n">
-        <v>182.75</v>
+        <v>184.1538461538462</v>
       </c>
       <c r="BO2" t="n">
-        <v>81.09999999999999</v>
+        <v>75.69230769230769</v>
       </c>
       <c r="BP2" t="n">
-        <v>109250</v>
+        <v>54384.61538461538</v>
       </c>
       <c r="BQ2" t="n">
-        <v>39965000</v>
+        <v>8730769.23076923</v>
       </c>
       <c r="BR2" t="n">
-        <v>83.5</v>
+        <v>78.23076923076923</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.6</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="BT2" t="n">
-        <v>24.7</v>
+        <v>28.13333333333333</v>
       </c>
       <c r="BU2" t="n">
-        <v>181.55</v>
+        <v>184.1333333333333</v>
       </c>
       <c r="BV2" t="n">
-        <v>78.84999999999999</v>
+        <v>74.86666666666666</v>
       </c>
       <c r="BW2" t="n">
-        <v>100550</v>
+        <v>64733.33333333334</v>
       </c>
       <c r="BX2" t="n">
-        <v>27802500</v>
+        <v>9515000</v>
       </c>
       <c r="BY2" t="n">
-        <v>82.40000000000001</v>
+        <v>75.93333333333334</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CA2" t="n">
-        <v>26</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="CB2" t="n">
-        <v>180.5</v>
+        <v>181</v>
       </c>
       <c r="CC2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CD2" t="n">
-        <v>167</v>
+        <v>235</v>
       </c>
       <c r="CE2" t="n">
-        <v>191000</v>
+        <v>212000</v>
       </c>
       <c r="CF2" t="n">
-        <v>86000000</v>
+        <v>52500000</v>
       </c>
       <c r="CG2" t="n">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="CH2" t="n">
         <v>6</v>
       </c>
       <c r="CI2" t="n">
-        <v>22</v>
+        <v>26.5</v>
       </c>
       <c r="CJ2" t="n">
-        <v>184.6666666666667</v>
+        <v>187</v>
       </c>
       <c r="CK2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CL2" t="n">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="CM2" t="n">
-        <v>237000</v>
+        <v>209000</v>
       </c>
       <c r="CN2" t="n">
-        <v>54500000</v>
+        <v>39400000</v>
       </c>
       <c r="CO2" t="n">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="CP2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>Aau4hOTh</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45588.66666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">davies a 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31750</v>
+        <v>34742</v>
       </c>
       <c r="F3" t="n">
-        <v>31319</v>
+        <v>24303</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.71</v>
-      </c>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="N3" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
-        <v>8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>5</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AG3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>1</v>
       </c>
-      <c r="AK3" t="n">
-        <v>216</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>731</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>139</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>651</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3</v>
-      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AU3" t="n">
         <v>48</v>
       </c>
       <c r="AV3" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1367,212 +1343,212 @@
         <v>20242025</v>
       </c>
       <c r="AY3" t="n">
-        <v>27</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="AZ3" t="n">
-        <v>185</v>
+        <v>184.2222222222222</v>
       </c>
       <c r="BA3" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>24222.22222222222</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2833333.333333333</v>
+      </c>
+      <c r="BD3" t="n">
         <v>78</v>
       </c>
-      <c r="BB3" t="n">
-        <v>58500</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>15050000</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>81</v>
-      </c>
       <c r="BE3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BF3" t="n">
-        <v>26.11111111111111</v>
+        <v>23.45454545454545</v>
       </c>
       <c r="BG3" t="n">
-        <v>180.7777777777778</v>
+        <v>184.4545454545455</v>
       </c>
       <c r="BH3" t="n">
-        <v>84.88888888888889</v>
+        <v>69.27272727272727</v>
       </c>
       <c r="BI3" t="n">
-        <v>194444.4444444444</v>
+        <v>32363.63636363636</v>
       </c>
       <c r="BJ3" t="n">
-        <v>65444444.44444445</v>
+        <v>2743181.818181818</v>
       </c>
       <c r="BK3" t="n">
-        <v>87.22222222222223</v>
+        <v>75.72727272727273</v>
       </c>
       <c r="BL3" t="n">
-        <v>3.555555555555555</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>27.5</v>
+        <v>24.52941176470588</v>
       </c>
       <c r="BN3" t="n">
-        <v>177</v>
+        <v>180.2941176470588</v>
       </c>
       <c r="BO3" t="n">
-        <v>75.5</v>
+        <v>70.11764705882354</v>
       </c>
       <c r="BP3" t="n">
-        <v>53000</v>
+        <v>25058.82352941177</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9712500</v>
+        <v>2514705.882352941</v>
       </c>
       <c r="BR3" t="n">
-        <v>77.625</v>
+        <v>75.35294117647059</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.625</v>
+        <v>1</v>
       </c>
       <c r="BT3" t="n">
-        <v>26.41176470588235</v>
+        <v>23.77272727272727</v>
       </c>
       <c r="BU3" t="n">
-        <v>180.2941176470588</v>
+        <v>178.1363636363636</v>
       </c>
       <c r="BV3" t="n">
-        <v>79.76470588235294</v>
+        <v>68.90909090909091</v>
       </c>
       <c r="BW3" t="n">
-        <v>139705.8823529412</v>
+        <v>33090.90909090909</v>
       </c>
       <c r="BX3" t="n">
-        <v>41235294.11764706</v>
+        <v>2862500</v>
       </c>
       <c r="BY3" t="n">
-        <v>82.64705882352941</v>
+        <v>74.31818181818181</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.470588235294118</v>
+        <v>1</v>
       </c>
       <c r="CA3" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>184.1666666666667</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>6</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>416</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>138000</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>443</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI3" t="n">
         <v>26</v>
       </c>
-      <c r="CB3" t="n">
-        <v>188.2</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>5</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>374</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>248000</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>41800000</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>393</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>7</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>26.66666666666667</v>
-      </c>
       <c r="CJ3" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="CK3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CL3" t="n">
-        <v>238</v>
+        <v>71</v>
       </c>
       <c r="CM3" t="n">
-        <v>408000</v>
+        <v>40000</v>
       </c>
       <c r="CN3" t="n">
-        <v>86000000</v>
+        <v>2200000</v>
       </c>
       <c r="CO3" t="n">
-        <v>251</v>
+        <v>72</v>
       </c>
       <c r="CP3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6i2uTnqp</t>
+          <t>bLBozsEO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.45833333334</v>
+        <v>45588.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley r 
+          <t xml:space="preserve">busby j 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25586</v>
+        <v>31367</v>
       </c>
       <c r="F4" t="n">
-        <v>23072</v>
+        <v>13647</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -1583,34 +1559,34 @@
         <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
@@ -1622,12 +1598,12 @@
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>IPNnvzM7</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>pYaUUJs1</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AU4" t="n">
@@ -1642,123 +1618,2825 @@
       <c r="AX4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>20600</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2330000</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1</v>
+      </c>
       <c r="BF4" t="n">
-        <v>22.88888888888889</v>
+        <v>26.5</v>
       </c>
       <c r="BG4" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>29600</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2120000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>27.68421052631579</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>180.3684210526316</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>69.73684210526316</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>20578.94736842105</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1827631.578947368</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>71.94736842105263</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>25.73684210526316</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>179.7894736842105</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>70.52631578947368</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>32684.21052631579</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>73.42105263157895</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="CB4" t="n">
         <v>181.3333333333333</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="CC4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>196</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>47000</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>4075000</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>222</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>191</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>142</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>62000</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>145</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jypdPPa6</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45588.65625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whitestone d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>25586</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20168</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>40</v>
+      </c>
+      <c r="N5" t="n">
+        <v>60</v>
+      </c>
+      <c r="O5" t="n">
+        <v>11</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>37000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>5055555.555555556</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>78.66666666666667</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>23.9375</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>179.6875</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>70</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>27375</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>2706250</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>26.58823529411765</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>183.9411764705882</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>69.88235294117646</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>39176.47058823529</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>2439705.882352941</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>74.17647058823529</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>22</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>186</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>257</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>67000</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>292</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>438</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>251000</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>22100000</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>450</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2Zydfpat</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45588.65625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nield t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kenilworth road
+  luton </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11332</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>56</v>
+      </c>
+      <c r="N6" t="n">
+        <v>44</v>
+      </c>
+      <c r="O6" t="n">
+        <v>20</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>27.11111111111111</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>185</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>27000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4277777.777777778</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>69</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>21111.11111111111</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2766666.666666667</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>67.73333333333333</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>23200</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1855000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>72.46666666666667</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>66.46666666666667</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>15733.33333333333</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1658000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>73.93333333333334</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>347</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>112000</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>15225000</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>378</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>22</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>5</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>329</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>87000</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>9250000</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>382</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6RYCj2b5</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45588.65625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the den
+  london </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20146</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13954</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>41</v>
+      </c>
+      <c r="N7" t="n">
+        <v>59</v>
+      </c>
+      <c r="O7" t="n">
+        <v>14</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>180.5555555555555</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>27777.77777777778</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1777777.777777778</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>9700</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>2622500</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>25.8125</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>179.5625</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>67.8125</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>23500</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>181.3636363636364</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>67.90909090909091</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>17454.54545454546</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1543181.818181818</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>71.54545454545455</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>25</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>183</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>202</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>76000</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>218</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>27</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>192</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>134</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>139</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Ao0VwPEa</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45587.66666666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loftus road
+  london </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>18439</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14173</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>46</v>
+      </c>
+      <c r="N8" t="n">
+        <v>54</v>
+      </c>
+      <c r="O8" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>29200</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>4030000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>178.7272727272727</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>21727.27272727273</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1881818.181818182</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>181.7777777777778</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>27500</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>2715277.777777778</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>180</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>133</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>21000</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>144</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>31</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>183</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>70</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>70</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KfdOaoV7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45587.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>33280</v>
+      </c>
+      <c r="F9" t="n">
+        <v>18534</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>54</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46</v>
+      </c>
+      <c r="O9" t="n">
+        <v>25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>dIE1p27R</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>26.72727272727273</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>183.6363636363636</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>13636.36363636364</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2313636.363636364</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>182</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>14625</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1315625</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>26.78947368421053</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>179.8421052631579</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>69.84210526315789</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>13578.94736842105</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1948684.210526316</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>71.31578947368421</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>25.61904761904762</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>182</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>65.19047619047619</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>11142.85714285714</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>998809.5238095238</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>70.47619047619048</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>23</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>184</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>264</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>66000</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>6975000</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>294</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>190</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>206</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>209</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CjY4N3UI</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45587.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">elland road
+  leeds </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37792</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34968</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>51</v>
+      </c>
+      <c r="N10" t="n">
+        <v>49</v>
+      </c>
+      <c r="O10" t="n">
+        <v>26</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>38125</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>184</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>68.27272727272727</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>18818.18181818182</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>72.63636363636364</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>175.3</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>53100</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>7085000</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>68.625</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>19125</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1746875</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>73.375</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>225</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>127000</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>23400000</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>238</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>23</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>178</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>69</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>73</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ImLjo7MP</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45587.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11423</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" t="n">
+        <v>50</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>10700</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>27.55555555555556</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BH11" t="n">
         <v>68.88888888888889</v>
       </c>
-      <c r="BI4" t="n">
-        <v>20888.88888888889</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>2733333.333333333</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>77.22222222222223</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>24.07142857142857</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>180.4285714285714</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>69.28571428571429</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>26571.42857142857</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>2385714.285714286</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>74.57142857142857</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>25.08333333333333</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>179.0833333333333</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>68</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>17583.33333333333</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1872500</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>72.66666666666667</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>22</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>186</v>
-      </c>
-      <c r="CC4" t="n">
+      <c r="BI11" t="n">
+        <v>13777.77777777778</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1427777.777777778</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>26.04545454545455</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>66.54545454545455</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>10636.36363636364</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1164772.727272727</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>69.40909090909091</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>28.3125</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>184.8125</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>66.875</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>24312.5</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1092187.5</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>68.6875</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>31.66666666666667</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>182</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>205</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>27000</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>206</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>386</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>97000</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>6375000</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>436</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>xY1Nuopm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45587.65625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">finnie w 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deepdale
+  preston </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23408</v>
+      </c>
+      <c r="F12" t="n">
+        <v>13677</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>31</v>
+      </c>
+      <c r="N12" t="n">
+        <v>69</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="n">
         <v>4</v>
       </c>
-      <c r="CD4" t="n">
-        <v>257</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>67000</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>292</v>
-      </c>
-      <c r="CH4" t="n">
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>71</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>41555.55555555555</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6644444.444444444</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>73.55555555555556</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>68.54545454545455</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>22909.09090909091</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2071818.181818182</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>182</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>66.81818181818181</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>25272.72727272727</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1554545.454545455</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>74.09090909090909</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>187.25</v>
+      </c>
+      <c r="CC12" t="n">
         <v>4</v>
       </c>
-      <c r="CI4" t="n">
-        <v>22</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>180.8</v>
-      </c>
-      <c r="CK4" t="n">
+      <c r="CD12" t="n">
+        <v>274</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>93000</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>4825000</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>279</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>28</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>6</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>426</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>144000</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>441</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0jZANlNE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45587.65625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donohue m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hillsborough
+  sheffield </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39732</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22452</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>36</v>
+      </c>
+      <c r="N13" t="n">
+        <v>64</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH13" t="n">
         <v>5</v>
       </c>
-      <c r="CL4" t="n">
-        <v>329</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>87000</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>9250000</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>382</v>
-      </c>
-      <c r="CP4" t="n">
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="AU13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>10700</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1745000</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="n">
+        <v>27.26315789473684</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>182.7894736842105</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>67.52631578947368</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9631.578947368422</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1321052.631578947</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>26.76470588235294</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>178.2941176470588</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>67.47058823529412</v>
+      </c>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="n">
+        <v>1387647.058823529</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>72.17647058823529</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>139</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>139</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>178</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>136</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>34000</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>140</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6Dgvx3qC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45587.65625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bet365 stadium
+  stoke on trent </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30089</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19679</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>53</v>
+      </c>
+      <c r="N14" t="n">
+        <v>47</v>
+      </c>
+      <c r="O14" t="n">
+        <v>11</v>
+      </c>
+      <c r="P14" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>10</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
         <v>5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>KOLbZJEd</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="AU14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>69</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>20900</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1927500</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>24.0625</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>180.375</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>66.375</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>25625</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1465625</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>73.125</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>180.0714285714286</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>22214.28571428571</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1392857.142857143</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>74.07142857142857</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>26</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>179</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>204</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>79000</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>215</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>23</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>179</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>133</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>41000</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>150</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
